--- a/experiments/heavy_snow_experiments.xlsx
+++ b/experiments/heavy_snow_experiments.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="71" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="167" uniqueCount="46">
   <si>
     <t>group</t>
   </si>
@@ -70,16 +70,25 @@
     <t>-</t>
   </si>
   <si>
+    <t>36.3234</t>
+  </si>
+  <si>
+    <t>34.3820</t>
+  </si>
+  <si>
     <t>group2</t>
   </si>
   <si>
     <t>42</t>
   </si>
   <si>
-    <t>4,3,15,14,5</t>
-  </si>
-  <si>
-    <t>46,47,56,57,58</t>
+    <t>9,12</t>
+  </si>
+  <si>
+    <t>3,15,14,5</t>
+  </si>
+  <si>
+    <t>47,56,57,58</t>
   </si>
   <si>
     <t>54,55</t>
@@ -88,10 +97,10 @@
     <t>group3</t>
   </si>
   <si>
-    <t>4,3,18,14,5</t>
-  </si>
-  <si>
-    <t>46,47,54,57,58</t>
+    <t>3,18,14,5</t>
+  </si>
+  <si>
+    <t>47,54,57,58</t>
   </si>
   <si>
     <t>55,56</t>
@@ -100,31 +109,55 @@
     <t>group4</t>
   </si>
   <si>
-    <t>4,3,20,14,5</t>
-  </si>
-  <si>
-    <t>46,47,55,57,58</t>
+    <t>3,20,14,5</t>
+  </si>
+  <si>
+    <t>47,55,57,58</t>
   </si>
   <si>
     <t>54,56</t>
   </si>
   <si>
-    <t>average(14)</t>
-  </si>
-  <si>
-    <t>9.1658</t>
-  </si>
-  <si>
-    <t>7.8392</t>
+    <t/>
+  </si>
+  <si>
+    <t>group5</t>
+  </si>
+  <si>
+    <t>43</t>
+  </si>
+  <si>
+    <t>group6</t>
+  </si>
+  <si>
+    <t>group7</t>
+  </si>
+  <si>
+    <t>group8</t>
+  </si>
+  <si>
+    <t>group9</t>
+  </si>
+  <si>
+    <t>44</t>
+  </si>
+  <si>
+    <t>group10</t>
+  </si>
+  <si>
+    <t>group11</t>
+  </si>
+  <si>
+    <t>group12</t>
+  </si>
+  <si>
+    <t>average(0)</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="0.0000"/>
-  </numFmts>
   <fonts count="4" x14ac:knownFonts="1">
     <font>
       <color theme="1"/>
@@ -200,7 +233,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -216,9 +249,6 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="3" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -238,8 +268,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="HeavySnowExperiments" displayName="HeavySnowExperiments" ref="A1:L5" totalsRowShown="0">
-  <autoFilter ref="A1:L5">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="HeavySnowExperiments" displayName="HeavySnowExperiments" ref="A1:L12" totalsRowShown="0">
+  <autoFilter ref="A1:L12">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
     <filterColumn colId="2" hiddenButton="1"/>
@@ -273,7 +303,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:L6"/>
+  <dimension ref="A1:L13"/>
   <sheetFormatPr defaultRowHeight="20" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
@@ -343,207 +373,577 @@
       </c>
       <c r="G2" s="3" t="inlineStr">
         <is>
-          <t>23.5091</t>
+          <t>23.0909</t>
         </is>
       </c>
       <c r="H2" s="3" t="inlineStr">
         <is>
-          <t>22.3105</t>
-        </is>
-      </c>
-      <c r="I2" s="3" t="inlineStr">
-        <is>
-          <t>36.3234</t>
-        </is>
-      </c>
-      <c r="J2" s="3" t="inlineStr">
-        <is>
-          <t>34.3820</t>
-        </is>
+          <t>21.7814</t>
+        </is>
+      </c>
+      <c r="I2" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="J2" s="3" t="s">
+        <v>19</v>
       </c>
       <c r="K2" s="3" t="inlineStr">
         <is>
-          <t>12.8143</t>
+          <t>13.2325</t>
         </is>
       </c>
       <c r="L2" s="3" t="inlineStr">
         <is>
-          <t>12.0715</t>
+          <t>12.6006</t>
         </is>
       </c>
     </row>
     <row r="3" ht="22" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="G3" s="3" t="inlineStr">
         <is>
-          <t>41.0444</t>
+          <t>39.4445</t>
         </is>
       </c>
       <c r="H3" s="3" t="inlineStr">
         <is>
-          <t>38.4844</t>
+          <t>36.4387</t>
         </is>
       </c>
       <c r="I3" s="3" t="inlineStr">
         <is>
-          <t>46.4537</t>
+          <t>43.3634</t>
         </is>
       </c>
       <c r="J3" s="3" t="inlineStr">
         <is>
-          <t>40.9586</t>
+          <t>38.8708</t>
         </is>
       </c>
       <c r="K3" s="3" t="inlineStr">
         <is>
-          <t>5.4093</t>
+          <t>3.9189</t>
         </is>
       </c>
       <c r="L3" s="3" t="inlineStr">
         <is>
-          <t>2.4742</t>
+          <t>2.4321</t>
         </is>
       </c>
     </row>
     <row r="4" ht="22" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="G4" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="H4" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="I4" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="J4" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="K4" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="L4" s="3" t="s">
-        <v>17</v>
+        <v>29</v>
+      </c>
+      <c r="G4" s="3" t="inlineStr">
+        <is>
+          <t>44.7839</t>
+        </is>
+      </c>
+      <c r="H4" s="3" t="inlineStr">
+        <is>
+          <t>39.6598</t>
+        </is>
+      </c>
+      <c r="I4" s="3" t="inlineStr">
+        <is>
+          <t>47.1856</t>
+        </is>
+      </c>
+      <c r="J4" s="3" t="inlineStr">
+        <is>
+          <t>42.8409</t>
+        </is>
+      </c>
+      <c r="K4" s="3" t="inlineStr">
+        <is>
+          <t>2.4017</t>
+        </is>
+      </c>
+      <c r="L4" s="3" t="inlineStr">
+        <is>
+          <t>3.1811</t>
+        </is>
       </c>
     </row>
     <row r="5" ht="22" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="E5" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="F5" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="G5" s="3" t="inlineStr">
+        <is>
+          <t>38.4671</t>
+        </is>
+      </c>
+      <c r="H5" s="3" t="inlineStr">
+        <is>
+          <t>33.0774</t>
+        </is>
+      </c>
+      <c r="I5" s="3" t="inlineStr">
+        <is>
+          <t>37.8243</t>
+        </is>
+      </c>
+      <c r="J5" s="3" t="inlineStr">
+        <is>
+          <t>32.4623</t>
+        </is>
+      </c>
+      <c r="K5" s="3" t="inlineStr">
+        <is>
+          <t>-0.6428</t>
+        </is>
+      </c>
+      <c r="L5" s="3" t="inlineStr">
+        <is>
+          <t>-0.6151</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="22" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A6" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="F6" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="G6" s="3" t="inlineStr">
+        <is>
+          <t>22.2008</t>
+        </is>
+      </c>
+      <c r="H6" s="3" t="inlineStr">
+        <is>
+          <t>21.1579</t>
+        </is>
+      </c>
+      <c r="I6" s="3" t="inlineStr">
+        <is>
+          <t>32.1358</t>
+        </is>
+      </c>
+      <c r="J6" s="3" t="inlineStr">
+        <is>
+          <t>30.8829</t>
+        </is>
+      </c>
+      <c r="K6" s="3" t="inlineStr">
+        <is>
+          <t>9.9350</t>
+        </is>
+      </c>
+      <c r="L6" s="3" t="inlineStr">
+        <is>
+          <t>9.7250</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="22" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A7" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="E7" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="F7" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="G7" s="3" t="inlineStr">
+        <is>
+          <t>42.0868</t>
+        </is>
+      </c>
+      <c r="H7" s="3" t="inlineStr">
+        <is>
+          <t>38.2883</t>
+        </is>
+      </c>
+      <c r="I7" s="3" t="inlineStr">
+        <is>
+          <t>47.7948</t>
+        </is>
+      </c>
+      <c r="J7" s="3" t="inlineStr">
+        <is>
+          <t>42.2176</t>
+        </is>
+      </c>
+      <c r="K7" s="3" t="inlineStr">
+        <is>
+          <t>5.7080</t>
+        </is>
+      </c>
+      <c r="L7" s="3" t="inlineStr">
+        <is>
+          <t>3.9293</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="22" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A8" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="D8" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="B5" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="C5" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="D5" s="3" t="s">
+      <c r="E8" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="E5" s="3" t="s">
+      <c r="F8" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="F5" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="G5" s="3" t="s">
+      <c r="G8" s="3" t="inlineStr">
+        <is>
+          <t>45.4611</t>
+        </is>
+      </c>
+      <c r="H8" s="3" t="inlineStr">
+        <is>
+          <t>40.2651</t>
+        </is>
+      </c>
+      <c r="I8" s="3" t="inlineStr">
+        <is>
+          <t>49.7122</t>
+        </is>
+      </c>
+      <c r="J8" s="3" t="inlineStr">
+        <is>
+          <t>44.1453</t>
+        </is>
+      </c>
+      <c r="K8" s="3" t="inlineStr">
+        <is>
+          <t>4.2511</t>
+        </is>
+      </c>
+      <c r="L8" s="3" t="inlineStr">
+        <is>
+          <t>3.8802</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="22" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A9" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="D9" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="E9" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="F9" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="G9" s="3" t="inlineStr">
+        <is>
+          <t>38.2958</t>
+        </is>
+      </c>
+      <c r="H9" s="3" t="inlineStr">
+        <is>
+          <t>33.6474</t>
+        </is>
+      </c>
+      <c r="I9" s="3" t="inlineStr">
+        <is>
+          <t>44.0943</t>
+        </is>
+      </c>
+      <c r="J9" s="3" t="inlineStr">
+        <is>
+          <t>37.4557</t>
+        </is>
+      </c>
+      <c r="K9" s="3" t="inlineStr">
+        <is>
+          <t>5.7985</t>
+        </is>
+      </c>
+      <c r="L9" s="3" t="inlineStr">
+        <is>
+          <t>3.8083</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="22" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A10" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="D10" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="E10" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="F10" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="G10" s="3" t="inlineStr">
+        <is>
+          <t>49.9623</t>
+        </is>
+      </c>
+      <c r="H10" s="3" t="inlineStr">
+        <is>
+          <t>45.9375</t>
+        </is>
+      </c>
+      <c r="I10" s="3" t="inlineStr">
+        <is>
+          <t>55.8480</t>
+        </is>
+      </c>
+      <c r="J10" s="3" t="inlineStr">
+        <is>
+          <t>49.4888</t>
+        </is>
+      </c>
+      <c r="K10" s="3" t="inlineStr">
+        <is>
+          <t>5.8857</t>
+        </is>
+      </c>
+      <c r="L10" s="3" t="inlineStr">
+        <is>
+          <t>3.5513</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="22" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A11" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="D11" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="E11" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="F11" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="G11" s="3" t="inlineStr">
+        <is>
+          <t>49.0521</t>
+        </is>
+      </c>
+      <c r="H11" s="3" t="inlineStr">
+        <is>
+          <t>44.6235</t>
+        </is>
+      </c>
+      <c r="I11" s="3" t="inlineStr">
+        <is>
+          <t>46.2094</t>
+        </is>
+      </c>
+      <c r="J11" s="3" t="inlineStr">
+        <is>
+          <t>39.0185</t>
+        </is>
+      </c>
+      <c r="K11" s="3" t="inlineStr">
+        <is>
+          <t>-2.8427</t>
+        </is>
+      </c>
+      <c r="L11" s="3" t="inlineStr">
+        <is>
+          <t>-5.6050</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="22" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A12" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="D12" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="E12" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="F12" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="G12" s="3" t="inlineStr">
+        <is>
+          <t>41.4402</t>
+        </is>
+      </c>
+      <c r="H12" s="3" t="inlineStr">
+        <is>
+          <t>35.3763</t>
+        </is>
+      </c>
+      <c r="I12" s="3" t="inlineStr">
+        <is>
+          <t>49.3879</t>
+        </is>
+      </c>
+      <c r="J12" s="3" t="inlineStr">
+        <is>
+          <t>42.3528</t>
+        </is>
+      </c>
+      <c r="K12" s="3" t="inlineStr">
+        <is>
+          <t>7.9477</t>
+        </is>
+      </c>
+      <c r="L12" s="3" t="inlineStr">
+        <is>
+          <t>6.9765</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="22" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>average(11)</t>
+        </is>
+      </c>
+      <c r="B13" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="H5" s="3" t="s">
+      <c r="C13" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="I5" s="3" t="s">
+      <c r="D13" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="J5" s="3" t="s">
+      <c r="E13" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="K5" s="3" t="s">
+      <c r="F13" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="L5" s="3" t="s">
+      <c r="G13" s="5" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="6" ht="22" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A6" s="4" t="inlineStr">
-        <is>
-          <t>average(2)</t>
-        </is>
-      </c>
-      <c r="B6" s="5" t="s">
+      <c r="H13" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="C6" s="5" t="s">
+      <c r="I13" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="D6" s="5" t="s">
+      <c r="J13" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="E6" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="F6" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="G6" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="H6" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="I6" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="J6" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="K6" s="5" t="inlineStr">
-        <is>
-          <t>9.1118</t>
-        </is>
-      </c>
-      <c r="L6" s="5" t="inlineStr">
-        <is>
-          <t>7.2728</t>
+      <c r="K13" s="5" t="inlineStr">
+        <is>
+          <t>5.0540</t>
+        </is>
+      </c>
+      <c r="L13" s="5" t="inlineStr">
+        <is>
+          <t>3.9877</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:L5"/>
+  <autoFilter ref="A1:L12"/>
   <pageMargins left="0.3" right="0.3" top="0.5" bottom="0.5" header="0.2" footer="0.2"/>
   <pageSetup orientation="landscape" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="0" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
   <tableParts count="1">
